--- a/database/SPX.xlsx
+++ b/database/SPX.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2580"/>
+  <dimension ref="A1:F2581"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52027,6 +52027,26 @@
         <v>3473000943</v>
       </c>
     </row>
+    <row r="2581">
+      <c r="A2581" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B2581" t="n">
+        <v>7805.96</v>
+      </c>
+      <c r="C2581" t="n">
+        <v>7844.52</v>
+      </c>
+      <c r="D2581" t="n">
+        <v>7805.96</v>
+      </c>
+      <c r="E2581" t="n">
+        <v>7818.93</v>
+      </c>
+      <c r="F2581" t="n">
+        <v>2717394878</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/SPX.xlsx
+++ b/database/SPX.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2581"/>
+  <dimension ref="A1:F2582"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52047,6 +52047,26 @@
         <v>2717394878</v>
       </c>
     </row>
+    <row r="2582">
+      <c r="A2582" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B2582" t="n">
+        <v>7792.98</v>
+      </c>
+      <c r="C2582" t="n">
+        <v>7807.02</v>
+      </c>
+      <c r="D2582" t="n">
+        <v>7763.34</v>
+      </c>
+      <c r="E2582" t="n">
+        <v>7801.77</v>
+      </c>
+      <c r="F2582" t="n">
+        <v>2648837293</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/SPX.xlsx
+++ b/database/SPX.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2582"/>
+  <dimension ref="A1:F2583"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52067,6 +52067,26 @@
         <v>2648837293</v>
       </c>
     </row>
+    <row r="2583">
+      <c r="A2583" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B2583" t="n">
+        <v>7778.45</v>
+      </c>
+      <c r="C2583" t="n">
+        <v>7797.79</v>
+      </c>
+      <c r="D2583" t="n">
+        <v>7731.26</v>
+      </c>
+      <c r="E2583" t="n">
+        <v>7765.36</v>
+      </c>
+      <c r="F2583" t="n">
+        <v>3518934024</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/SPX.xlsx
+++ b/database/SPX.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2583"/>
+  <dimension ref="A1:F2584"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52087,6 +52087,26 @@
         <v>3518934024</v>
       </c>
     </row>
+    <row r="2584">
+      <c r="A2584" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B2584" t="n">
+        <v>7786.36</v>
+      </c>
+      <c r="C2584" t="n">
+        <v>7820.57</v>
+      </c>
+      <c r="D2584" t="n">
+        <v>7779.34</v>
+      </c>
+      <c r="E2584" t="n">
+        <v>7811.54</v>
+      </c>
+      <c r="F2584" t="n">
+        <v>2645750862</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/SPX.xlsx
+++ b/database/SPX.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2584"/>
+  <dimension ref="A1:F2585"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52107,6 +52107,26 @@
         <v>2645750862</v>
       </c>
     </row>
+    <row r="2585">
+      <c r="A2585" s="1" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B2585" t="n">
+        <v>7813.04</v>
+      </c>
+      <c r="C2585" t="n">
+        <v>7821.67</v>
+      </c>
+      <c r="D2585" t="n">
+        <v>7796.94</v>
+      </c>
+      <c r="E2585" t="n">
+        <v>7807.24</v>
+      </c>
+      <c r="F2585" t="n">
+        <v>2291949104</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/SPX.xlsx
+++ b/database/SPX.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2585"/>
+  <dimension ref="A1:F2586"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52127,6 +52127,26 @@
         <v>2291949104</v>
       </c>
     </row>
+    <row r="2586">
+      <c r="A2586" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B2586" t="n">
+        <v>7795.27</v>
+      </c>
+      <c r="C2586" t="n">
+        <v>7814.15</v>
+      </c>
+      <c r="D2586" t="n">
+        <v>7786.11</v>
+      </c>
+      <c r="E2586" t="n">
+        <v>7805.45</v>
+      </c>
+      <c r="F2586" t="n">
+        <v>2640232610</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/SPX.xlsx
+++ b/database/SPX.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2586"/>
+  <dimension ref="A1:F2587"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52147,6 +52147,26 @@
         <v>2640232610</v>
       </c>
     </row>
+    <row r="2587">
+      <c r="A2587" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B2587" t="n">
+        <v>7774.18</v>
+      </c>
+      <c r="C2587" t="n">
+        <v>7789.15</v>
+      </c>
+      <c r="D2587" t="n">
+        <v>7693.31</v>
+      </c>
+      <c r="E2587" t="n">
+        <v>7718.94</v>
+      </c>
+      <c r="F2587" t="n">
+        <v>3388032960</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/SPX.xlsx
+++ b/database/SPX.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2587"/>
+  <dimension ref="A1:F2588"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52167,6 +52167,26 @@
         <v>3388032960</v>
       </c>
     </row>
+    <row r="2588">
+      <c r="A2588" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B2588" t="n">
+        <v>7687.31</v>
+      </c>
+      <c r="C2588" t="n">
+        <v>7754.15</v>
+      </c>
+      <c r="D2588" t="n">
+        <v>7669.66</v>
+      </c>
+      <c r="E2588" t="n">
+        <v>7744.06</v>
+      </c>
+      <c r="F2588" t="n">
+        <v>3428090891</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/SPX.xlsx
+++ b/database/SPX.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2588"/>
+  <dimension ref="A1:F2589"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52187,6 +52187,26 @@
         <v>3428090891</v>
       </c>
     </row>
+    <row r="2589">
+      <c r="A2589" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B2589" t="n">
+        <v>7745.32</v>
+      </c>
+      <c r="C2589" t="n">
+        <v>7756.84</v>
+      </c>
+      <c r="D2589" t="n">
+        <v>7631.77</v>
+      </c>
+      <c r="E2589" t="n">
+        <v>7659.44</v>
+      </c>
+      <c r="F2589" t="n">
+        <v>3319597424</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/SPX.xlsx
+++ b/database/SPX.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2589"/>
+  <dimension ref="A1:F2590"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52207,6 +52207,26 @@
         <v>3319597424</v>
       </c>
     </row>
+    <row r="2590">
+      <c r="A2590" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B2590" t="n">
+        <v>7702.77</v>
+      </c>
+      <c r="C2590" t="n">
+        <v>7731.18</v>
+      </c>
+      <c r="D2590" t="n">
+        <v>7684.79</v>
+      </c>
+      <c r="E2590" t="n">
+        <v>7690.73</v>
+      </c>
+      <c r="F2590" t="n">
+        <v>2634321389</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/SPX.xlsx
+++ b/database/SPX.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2590"/>
+  <dimension ref="A1:F2591"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52227,6 +52227,26 @@
         <v>2634321389</v>
       </c>
     </row>
+    <row r="2591">
+      <c r="A2591" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B2591" t="n">
+        <v>7679.01</v>
+      </c>
+      <c r="C2591" t="n">
+        <v>7748.42</v>
+      </c>
+      <c r="D2591" t="n">
+        <v>7668.03</v>
+      </c>
+      <c r="E2591" t="n">
+        <v>7712.57</v>
+      </c>
+      <c r="F2591" t="n">
+        <v>2721619490</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/SPX.xlsx
+++ b/database/SPX.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2591"/>
+  <dimension ref="A1:F2592"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52247,6 +52247,26 @@
         <v>2721619490</v>
       </c>
     </row>
+    <row r="2592">
+      <c r="A2592" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B2592" t="n">
+        <v>7736.43</v>
+      </c>
+      <c r="C2592" t="n">
+        <v>7770.4</v>
+      </c>
+      <c r="D2592" t="n">
+        <v>7709.34</v>
+      </c>
+      <c r="E2592" t="n">
+        <v>7757.17</v>
+      </c>
+      <c r="F2592" t="n">
+        <v>2889474867</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/SPX.xlsx
+++ b/database/SPX.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2592"/>
+  <dimension ref="A1:F2593"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52267,6 +52267,26 @@
         <v>2889474867</v>
       </c>
     </row>
+    <row r="2593">
+      <c r="A2593" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B2593" t="n">
+        <v>7694.62</v>
+      </c>
+      <c r="C2593" t="n">
+        <v>7702.94</v>
+      </c>
+      <c r="D2593" t="n">
+        <v>7637.36</v>
+      </c>
+      <c r="E2593" t="n">
+        <v>7663.43</v>
+      </c>
+      <c r="F2593" t="n">
+        <v>3559453335</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/SPX.xlsx
+++ b/database/SPX.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2593"/>
+  <dimension ref="A1:F2594"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52287,6 +52287,26 @@
         <v>3559453335</v>
       </c>
     </row>
+    <row r="2594">
+      <c r="A2594" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B2594" t="n">
+        <v>7637.18</v>
+      </c>
+      <c r="C2594" t="n">
+        <v>7660.15</v>
+      </c>
+      <c r="D2594" t="n">
+        <v>7612.07</v>
+      </c>
+      <c r="E2594" t="n">
+        <v>7623.68</v>
+      </c>
+      <c r="F2594" t="n">
+        <v>2749563255</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/SPX.xlsx
+++ b/database/SPX.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2594"/>
+  <dimension ref="A1:F2595"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52307,6 +52307,26 @@
         <v>2749563255</v>
       </c>
     </row>
+    <row r="2595">
+      <c r="A2595" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B2595" t="n">
+        <v>7639.7</v>
+      </c>
+      <c r="C2595" t="n">
+        <v>7702.13</v>
+      </c>
+      <c r="D2595" t="n">
+        <v>7639.7</v>
+      </c>
+      <c r="E2595" t="n">
+        <v>7676.77</v>
+      </c>
+      <c r="F2595" t="n">
+        <v>2759066886</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/SPX.xlsx
+++ b/database/SPX.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2595"/>
+  <dimension ref="A1:F2596"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52327,6 +52327,26 @@
         <v>2759066886</v>
       </c>
     </row>
+    <row r="2596">
+      <c r="A2596" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B2596" t="n">
+        <v>7699.47</v>
+      </c>
+      <c r="C2596" t="n">
+        <v>7736.24</v>
+      </c>
+      <c r="D2596" t="n">
+        <v>7677.16</v>
+      </c>
+      <c r="E2596" t="n">
+        <v>7722.6</v>
+      </c>
+      <c r="F2596" t="n">
+        <v>2810939049</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/SPX.xlsx
+++ b/database/SPX.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2596"/>
+  <dimension ref="A1:F2597"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52347,6 +52347,26 @@
         <v>2810939049</v>
       </c>
     </row>
+    <row r="2597">
+      <c r="A2597" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B2597" t="n">
+        <v>7735.56</v>
+      </c>
+      <c r="C2597" t="n">
+        <v>7758.43</v>
+      </c>
+      <c r="D2597" t="n">
+        <v>7718.37</v>
+      </c>
+      <c r="E2597" t="n">
+        <v>7743.98</v>
+      </c>
+      <c r="F2597" t="n">
+        <v>3085116637</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/SPX.xlsx
+++ b/database/SPX.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2597"/>
+  <dimension ref="A1:F2598"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52367,6 +52367,26 @@
         <v>3085116637</v>
       </c>
     </row>
+    <row r="2598">
+      <c r="A2598" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B2598" t="n">
+        <v>7699.61</v>
+      </c>
+      <c r="C2598" t="n">
+        <v>7732.21</v>
+      </c>
+      <c r="D2598" t="n">
+        <v>7690.94</v>
+      </c>
+      <c r="E2598" t="n">
+        <v>7720.39</v>
+      </c>
+      <c r="F2598" t="n">
+        <v>3300311487</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/SPX.xlsx
+++ b/database/SPX.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2598"/>
+  <dimension ref="A1:F2599"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52387,6 +52387,26 @@
         <v>3300311487</v>
       </c>
     </row>
+    <row r="2599">
+      <c r="A2599" s="1" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B2599" t="n">
+        <v>7631.07</v>
+      </c>
+      <c r="C2599" t="n">
+        <v>7637.48</v>
+      </c>
+      <c r="D2599" t="n">
+        <v>7527.56</v>
+      </c>
+      <c r="E2599" t="n">
+        <v>7580.07</v>
+      </c>
+      <c r="F2599" t="n">
+        <v>4268617866</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
